--- a/Indicator_Gen/Python Code/BLS/config/BLS_State and Area Employment_Series ID Codes.xlsx
+++ b/Indicator_Gen/Python Code/BLS/config/BLS_State and Area Employment_Series ID Codes.xlsx
@@ -5,19 +5,23 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfontes\Documents\Projects\Regional-Monitoring\Indicator_Gen\Python Code\BLS\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sacog.sharepoint.com/sites/RegionalMonitoringandReporting/Shared Documents/Process Revamp/Task 9. Collect new data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C827A8D1-5099-44F5-B9B2-74F9ABEEBBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="13_ncr:1_{D11369E1-5776-4A57-BFA2-F789D30C5E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0331B726-895D-47CF-B0B4-0580987959CF}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="2400" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="BLS_MSA" sheetId="4" r:id="rId1"/>
-    <sheet name="industry_codes" sheetId="1" r:id="rId2"/>
-    <sheet name="supersector_codes" sheetId="2" r:id="rId3"/>
-    <sheet name="datatype_codes" sheetId="3" r:id="rId4"/>
+    <sheet name="README" sheetId="5" r:id="rId1"/>
+    <sheet name="BLS_MSA" sheetId="4" r:id="rId2"/>
+    <sheet name="industry_codes" sheetId="1" r:id="rId3"/>
+    <sheet name="supersector_codes" sheetId="2" r:id="rId4"/>
+    <sheet name="datatype_codes" sheetId="3" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">industry_codes!$A$1:$G$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,15 +42,21 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={3DC759A5-1846-4E31-87D5-80254178482C}</author>
+    <author>tc={454F9C86-ABC5-4E87-9CCF-94F6AEF045EF}</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{3DC759A5-1846-4E31-87D5-80254178482C}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{454F9C86-ABC5-4E87-9CCF-94F6AEF045EF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+[Tasks]
+There is a task anchored to this comment that cannot be viewed in your client.
 Comment:
-    Use this as needed to combine multiple industries together into one overall category - may not need to do this since they seemed to already be categorized by 20000000, 3000000, etc...</t>
+    @Garett Ballard-Rosa Can you please fill out these mappings?
+Reply:
+    @Joshua Fontes cool, I finished the mapping. It gets a bit confusing at end with the government jobs. For example, we would need to subtract out the 'Fed Hospital' from the Fed total (since Fed Hospital being moved to the Health sector), and likewise local government we need to subtract out some so we not double counting.
+For state, there is a line for 'state gov excluding edu/health' that we use, but I need Jared to look into the two specific edu lines under state gov.
+Any questions either of you have, just ping me.</t>
       </text>
     </comment>
   </commentList>
@@ -90,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="844">
   <si>
     <t>industry_code</t>
   </si>
@@ -2508,6 +2518,120 @@
   </si>
   <si>
     <t>Total Jobs</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Jared - need to make sure that "Total Private" + "Government" = Total jobs that we will pull</t>
+  </si>
+  <si>
+    <t>Jared - Confirm that Agriculture is Total Private - Total Nonfarm</t>
+  </si>
+  <si>
+    <t>We are separating out Education and Health into different categories (also, Government has some jobs that are technically Education)</t>
+  </si>
+  <si>
+    <t>Removing some jobs here that should fall under Education</t>
+  </si>
+  <si>
+    <t>Jared - Make sure our categorizations/mappings for Education + Health + Government = the supersector codes of 65 + 90</t>
+  </si>
+  <si>
+    <t>TODO list:</t>
+  </si>
+  <si>
+    <t>then</t>
+  </si>
+  <si>
+    <t>Garett - map out industry codes into categories we want</t>
+  </si>
+  <si>
+    <t>Jared  - Confirm that the only geography level we can pull from for the CES survey is MSA</t>
+  </si>
+  <si>
+    <t>Jared - Confirm that "Total Private" + "Government" = Total jobs that we will pull</t>
+  </si>
+  <si>
+    <t>Jared - Make sure to also pull the national total</t>
+  </si>
+  <si>
+    <t>Additional notes:</t>
+  </si>
+  <si>
+    <t>Just want total number of jobs by MSA for only the peer regions</t>
+  </si>
+  <si>
+    <t>Jobs_2</t>
+  </si>
+  <si>
+    <t>Want to break out number of jobs by industry for our region and for the nation</t>
+  </si>
+  <si>
+    <t>Jobs_3</t>
+  </si>
+  <si>
+    <t>Indicator Name</t>
+  </si>
+  <si>
+    <t>Might create a new indicator - total jobs by select industry codes (see "industry_codes" tab)</t>
+  </si>
+  <si>
+    <t>This is the only data type we need for Regional Monitoring</t>
+  </si>
+  <si>
+    <t>Transportation, utilities, warehouse, wholesale</t>
+  </si>
+  <si>
+    <t>Retail</t>
+  </si>
+  <si>
+    <t>Finance, Information, Real Estate</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Leisure and Hospitaltity</t>
+  </si>
+  <si>
+    <t>Please double check here too. All Government is used in Jobs_3 to get at private/public split. But for Jobs_2, goverment is split into fed/state/local and also pulls out the edu and health components</t>
+  </si>
+  <si>
+    <t>Ditto to earlier comments, but make sure our state gov categorization is still summing</t>
+  </si>
+  <si>
+    <t>Can you look into row 335 and 339. Are these different or is one nested in the other?</t>
+  </si>
+  <si>
+    <t>This we would need to also subtract from the Jobs_2 local government</t>
+  </si>
+  <si>
+    <t>Jobs_1, Jobs_2, Jobs_3</t>
+  </si>
+  <si>
+    <t>Jobs_1, Jobs_3</t>
+  </si>
+  <si>
+    <t>This # needs to be less the fed gov hospitals (row 323)</t>
+  </si>
+  <si>
+    <t>Education?</t>
+  </si>
+  <si>
+    <t>Yes?</t>
+  </si>
+  <si>
+    <t>This we would also need to subtract from the Jobs_2 federal government so we not double counting</t>
+  </si>
+  <si>
+    <t>Dont think we need to subtract out for state, as they already did in their codes. But double check</t>
+  </si>
+  <si>
+    <t>This # needs to be less transportation (row337) and hospitals (row 338) and maybe elementary/secondary if that different than edu services</t>
   </si>
 </sst>
 </file>
@@ -2531,12 +2655,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
@@ -2551,8 +2669,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2568,6 +2692,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2599,7 +2729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2610,8 +2740,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2629,9 +2761,45 @@
 </styleSheet>
 </file>
 
+<file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
+  <Task id="{1E09C20A-2C29-42A6-B384-C8487428E36E}">
+    <Anchor>
+      <Comment id="{454F9C86-ABC5-4E87-9CCF-94F6AEF045EF}"/>
+    </Anchor>
+    <History>
+      <Event time="2024-05-01T23:15:51.48" id="{2ED0FD2D-0E9E-45A6-AA9D-1608FFE058D5}">
+        <Attribution userId="S::jfontes@sacog.org::79e59a1a-bb1e-46d8-b432-2fc051273d82" userName="Joshua Fontes" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{454F9C86-ABC5-4E87-9CCF-94F6AEF045EF}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2024-05-01T23:15:51.48" id="{7F4D39CE-EBAA-4EFD-A7A3-72CB21FAA7E9}">
+        <Attribution userId="S::jfontes@sacog.org::79e59a1a-bb1e-46d8-b432-2fc051273d82" userName="Joshua Fontes" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{454F9C86-ABC5-4E87-9CCF-94F6AEF045EF}"/>
+        </Anchor>
+        <Assign userId="S::GBallard@sacog.org::a3ced981-b971-479c-b3fc-ef3dcb451512" userName="Garett Ballard-Rosa" userProvider="AD"/>
+      </Event>
+      <Event time="2024-05-01T23:15:51.48" id="{F8F37238-8E3F-49C4-BF75-2EDAE8F9E33A}">
+        <Attribution userId="S::jfontes@sacog.org::79e59a1a-bb1e-46d8-b432-2fc051273d82" userName="Joshua Fontes" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{454F9C86-ABC5-4E87-9CCF-94F6AEF045EF}"/>
+        </Anchor>
+        <SetTitle title="@Garett Ballard-Rosa Can you please fill out these mappings?"/>
+      </Event>
+    </History>
+  </Task>
+</Tasks>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Joshua Fontes" id="{D0D33D92-0442-42C7-A5CF-0145CF8F052F}" userId="jfontes@sacog.org" providerId="PeoplePicker"/>
+  <person displayName="Garett Ballard-Rosa" id="{A7569C1A-363F-4C7D-8B92-EEA59AB52E73}" userId="GBallard@sacog.org" providerId="PeoplePicker"/>
   <person displayName="Joshua Fontes" id="{8E8C4343-8665-4A1B-BC2E-BCC5D4E8C218}" userId="S::jfontes@sacog.org::79e59a1a-bb1e-46d8-b432-2fc051273d82" providerId="AD"/>
+  <person displayName="Garett Ballard-Rosa" id="{1BD7E9C1-34BA-4F07-A029-4E07ACD40D6B}" userId="S::gballard@sacog.org::a3ced981-b971-479c-b3fc-ef3dcb451512" providerId="AD"/>
 </personList>
 </file>
 
@@ -2922,8 +3090,19 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C1" dT="2024-04-30T15:43:52.18" personId="{8E8C4343-8665-4A1B-BC2E-BCC5D4E8C218}" id="{3DC759A5-1846-4E31-87D5-80254178482C}">
-    <text>Use this as needed to combine multiple industries together into one overall category - may not need to do this since they seemed to already be categorized by 20000000, 3000000, etc...</text>
+  <threadedComment ref="D1" dT="2024-05-01T23:15:51.49" personId="{8E8C4343-8665-4A1B-BC2E-BCC5D4E8C218}" id="{454F9C86-ABC5-4E87-9CCF-94F6AEF045EF}">
+    <text>@Garett Ballard-Rosa Can you please fill out these mappings?</text>
+    <mentions>
+      <mention mentionpersonId="{A7569C1A-363F-4C7D-8B92-EEA59AB52E73}" mentionId="{10594758-0465-41B7-B5DC-7F3B8E885B5F}" startIndex="0" length="20"/>
+    </mentions>
+  </threadedComment>
+  <threadedComment ref="D1" dT="2024-05-01T23:57:08.31" personId="{1BD7E9C1-34BA-4F07-A029-4E07ACD40D6B}" id="{7E17EE5E-EA7A-4635-8600-427D85DD8AF8}" parentId="{454F9C86-ABC5-4E87-9CCF-94F6AEF045EF}">
+    <text>@Joshua Fontes cool, I finished the mapping. It gets a bit confusing at end with the government jobs. For example, we would need to subtract out the 'Fed Hospital' from the Fed total (since Fed Hospital being moved to the Health sector), and likewise local government we need to subtract out some so we not double counting.
+For state, there is a line for 'state gov excluding edu/health' that we use, but I need Jared to look into the two specific edu lines under state gov.
+Any questions either of you have, just ping me.</text>
+    <mentions>
+      <mention mentionpersonId="{D0D33D92-0442-42C7-A5CF-0145CF8F052F}" mentionId="{B02AA53A-A3BF-404E-811D-888139FBA803}" startIndex="0" length="14"/>
+    </mentions>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -2945,7 +3124,87 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49AA1604-14CD-498B-A715-431C164EE7F2}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>804</v>
+      </c>
+      <c r="B10" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>820</v>
+      </c>
+      <c r="B11" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>822</v>
+      </c>
+      <c r="B12" t="s">
+        <v>824</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37DED255-EA4D-40F9-9AF6-E3893C558276}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3233,17 +3492,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F341"/>
+  <sheetPr>
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:G341"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="99.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.1796875" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3251,74 +3514,95 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>736</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>342</v>
       </c>
-      <c r="D2" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>820</v>
+      </c>
+      <c r="E2" t="s">
+        <v>739</v>
+      </c>
+      <c r="G2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>343</v>
       </c>
-      <c r="D3" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>836</v>
+      </c>
+      <c r="E3" t="s">
+        <v>739</v>
+      </c>
+      <c r="G3" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>344</v>
       </c>
-      <c r="D4" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>822</v>
+      </c>
+      <c r="E4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>345</v>
       </c>
-      <c r="D5" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>822</v>
+      </c>
+      <c r="E5" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>346</v>
       </c>
-      <c r="D6" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E6" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -3326,123 +3610,126 @@
         <v>347</v>
       </c>
       <c r="C7" t="s">
+        <v>820</v>
+      </c>
+      <c r="D7" t="s">
         <v>347</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>348</v>
       </c>
-      <c r="D8" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E8" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>349</v>
       </c>
-      <c r="D9" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E9" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>350</v>
       </c>
-      <c r="D10" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E10" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>351</v>
       </c>
-      <c r="D11" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E11" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>352</v>
       </c>
-      <c r="D12" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E12" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>353</v>
       </c>
-      <c r="D13" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E13" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" t="s">
         <v>354</v>
       </c>
-      <c r="D14" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E14" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15" t="s">
         <v>355</v>
       </c>
-      <c r="D15" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E15" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>356</v>
       </c>
-      <c r="D16" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E16" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>357</v>
       </c>
-      <c r="D17" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E17" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -3450,1798 +3737,1822 @@
         <v>358</v>
       </c>
       <c r="C18" t="s">
+        <v>820</v>
+      </c>
+      <c r="D18" t="s">
         <v>358</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19" t="s">
         <v>359</v>
       </c>
-      <c r="D19" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E19" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
       <c r="B20" t="s">
         <v>360</v>
       </c>
-      <c r="D20" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E20" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>21</v>
       </c>
       <c r="B21" t="s">
         <v>361</v>
       </c>
-      <c r="D21" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E21" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>22</v>
       </c>
       <c r="B22" t="s">
         <v>362</v>
       </c>
-      <c r="D22" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E22" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>23</v>
       </c>
       <c r="B23" t="s">
         <v>363</v>
       </c>
-      <c r="D23" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E23" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
       <c r="B24" t="s">
         <v>364</v>
       </c>
-      <c r="D24" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E24" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>25</v>
       </c>
       <c r="B25" t="s">
         <v>365</v>
       </c>
-      <c r="D25" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E25" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26" t="s">
         <v>366</v>
       </c>
-      <c r="D26" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E26" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>27</v>
       </c>
       <c r="B27" t="s">
         <v>367</v>
       </c>
-      <c r="D27" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E27" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
         <v>368</v>
       </c>
-      <c r="D28" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E28" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>29</v>
       </c>
       <c r="B29" t="s">
         <v>369</v>
       </c>
-      <c r="D29" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E29" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>30</v>
       </c>
       <c r="B30" t="s">
         <v>370</v>
       </c>
-      <c r="D30" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E30" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>31</v>
       </c>
       <c r="B31" t="s">
         <v>371</v>
       </c>
-      <c r="D31" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E31" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>32</v>
       </c>
       <c r="B32" t="s">
         <v>372</v>
       </c>
+      <c r="C32" t="s">
+        <v>820</v>
+      </c>
       <c r="D32" t="s">
+        <v>372</v>
+      </c>
+      <c r="E32" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>33</v>
       </c>
       <c r="B33" t="s">
         <v>373</v>
       </c>
-      <c r="D33" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E33" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>34</v>
       </c>
       <c r="B34" t="s">
         <v>374</v>
       </c>
-      <c r="D34" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E34" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>35</v>
       </c>
       <c r="B35" t="s">
         <v>375</v>
       </c>
-      <c r="D35" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E35" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>36</v>
       </c>
       <c r="B36" t="s">
         <v>376</v>
       </c>
-      <c r="D36" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E36" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>37</v>
       </c>
       <c r="B37" t="s">
         <v>377</v>
       </c>
-      <c r="D37" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E37" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>38</v>
       </c>
       <c r="B38" t="s">
         <v>378</v>
       </c>
-      <c r="D38" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E38" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>39</v>
       </c>
       <c r="B39" t="s">
         <v>379</v>
       </c>
-      <c r="D39" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E39" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>40</v>
       </c>
       <c r="B40" t="s">
         <v>380</v>
       </c>
-      <c r="D40" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E40" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>41</v>
       </c>
       <c r="B41" t="s">
         <v>381</v>
       </c>
-      <c r="D41" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E41" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>42</v>
       </c>
       <c r="B42" t="s">
         <v>382</v>
       </c>
-      <c r="D42" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E42" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>43</v>
       </c>
       <c r="B43" t="s">
         <v>383</v>
       </c>
-      <c r="D43" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E43" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>44</v>
       </c>
       <c r="B44" t="s">
         <v>384</v>
       </c>
-      <c r="D44" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E44" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>45</v>
       </c>
       <c r="B45" t="s">
         <v>385</v>
       </c>
-      <c r="D45" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E45" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>46</v>
       </c>
       <c r="B46" t="s">
         <v>386</v>
       </c>
-      <c r="D46" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E46" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>47</v>
       </c>
       <c r="B47" t="s">
         <v>387</v>
       </c>
-      <c r="D47" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E47" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>48</v>
       </c>
       <c r="B48" t="s">
         <v>388</v>
       </c>
-      <c r="D48" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E48" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>49</v>
       </c>
       <c r="B49" t="s">
         <v>389</v>
       </c>
-      <c r="D49" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E49" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>50</v>
       </c>
       <c r="B50" t="s">
         <v>390</v>
       </c>
-      <c r="D50" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E50" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>51</v>
       </c>
       <c r="B51" t="s">
         <v>391</v>
       </c>
-      <c r="D51" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E51" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>52</v>
       </c>
       <c r="B52" t="s">
         <v>392</v>
       </c>
-      <c r="D52" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E52" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>53</v>
       </c>
       <c r="B53" t="s">
         <v>393</v>
       </c>
-      <c r="D53" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E53" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>54</v>
       </c>
       <c r="B54" t="s">
         <v>394</v>
       </c>
-      <c r="D54" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E54" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>55</v>
       </c>
       <c r="B55" t="s">
         <v>395</v>
       </c>
-      <c r="D55" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E55" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>56</v>
       </c>
       <c r="B56" t="s">
         <v>396</v>
       </c>
-      <c r="D56" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E56" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>57</v>
       </c>
       <c r="B57" t="s">
         <v>397</v>
       </c>
-      <c r="D57" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E57" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>58</v>
       </c>
       <c r="B58" t="s">
         <v>398</v>
       </c>
-      <c r="D58" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E58" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>59</v>
       </c>
       <c r="B59" t="s">
         <v>399</v>
       </c>
-      <c r="D59" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E59" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>60</v>
       </c>
       <c r="B60" t="s">
         <v>400</v>
       </c>
-      <c r="D60" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E60" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>61</v>
       </c>
       <c r="B61" t="s">
         <v>401</v>
       </c>
-      <c r="D61" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E61" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>62</v>
       </c>
       <c r="B62" t="s">
         <v>402</v>
       </c>
-      <c r="D62" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E62" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>63</v>
       </c>
       <c r="B63" t="s">
         <v>403</v>
       </c>
-      <c r="D63" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E63" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>64</v>
       </c>
       <c r="B64" t="s">
         <v>404</v>
       </c>
-      <c r="D64" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E64" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>65</v>
       </c>
       <c r="B65" t="s">
         <v>405</v>
       </c>
-      <c r="D65" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E65" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>66</v>
       </c>
       <c r="B66" t="s">
         <v>406</v>
       </c>
-      <c r="D66" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E66" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>67</v>
       </c>
       <c r="B67" t="s">
         <v>407</v>
       </c>
-      <c r="D67" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E67" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>68</v>
       </c>
       <c r="B68" t="s">
         <v>408</v>
       </c>
-      <c r="D68" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E68" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>69</v>
       </c>
       <c r="B69" t="s">
         <v>409</v>
       </c>
-      <c r="D69" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E69" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>70</v>
       </c>
       <c r="B70" t="s">
         <v>410</v>
       </c>
-      <c r="D70" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E70" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>71</v>
       </c>
       <c r="B71" t="s">
         <v>411</v>
       </c>
-      <c r="D71" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E71" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>72</v>
       </c>
       <c r="B72" t="s">
         <v>412</v>
       </c>
-      <c r="D72" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E72" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>73</v>
       </c>
       <c r="B73" t="s">
         <v>413</v>
       </c>
-      <c r="D73" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E73" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>74</v>
       </c>
       <c r="B74" t="s">
         <v>414</v>
       </c>
-      <c r="D74" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E74" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>75</v>
       </c>
       <c r="B75" t="s">
         <v>415</v>
       </c>
-      <c r="D75" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E75" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>76</v>
       </c>
       <c r="B76" t="s">
         <v>416</v>
       </c>
-      <c r="D76" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E76" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>77</v>
       </c>
       <c r="B77" t="s">
         <v>417</v>
       </c>
-      <c r="D77" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E77" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>78</v>
       </c>
       <c r="B78" t="s">
         <v>418</v>
       </c>
-      <c r="D78" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E78" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>79</v>
       </c>
       <c r="B79" t="s">
         <v>419</v>
       </c>
-      <c r="D79" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E79" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>80</v>
       </c>
       <c r="B80" t="s">
         <v>420</v>
       </c>
-      <c r="D80" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E80" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>81</v>
       </c>
       <c r="B81" t="s">
         <v>421</v>
       </c>
-      <c r="D81" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E81" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>82</v>
       </c>
       <c r="B82" t="s">
         <v>422</v>
       </c>
-      <c r="D82" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E82" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>83</v>
       </c>
       <c r="B83" t="s">
         <v>423</v>
       </c>
-      <c r="D83" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E83" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>84</v>
       </c>
       <c r="B84" t="s">
         <v>424</v>
       </c>
-      <c r="D84" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E84" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>85</v>
       </c>
       <c r="B85" t="s">
         <v>425</v>
       </c>
-      <c r="D85" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E85" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>86</v>
       </c>
       <c r="B86" t="s">
         <v>426</v>
       </c>
-      <c r="D86" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E86" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>87</v>
       </c>
       <c r="B87" t="s">
         <v>427</v>
       </c>
-      <c r="D87" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E87" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>88</v>
       </c>
       <c r="B88" t="s">
         <v>428</v>
       </c>
-      <c r="D88" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E88" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>89</v>
       </c>
       <c r="B89" t="s">
         <v>429</v>
       </c>
-      <c r="D89" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E89" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>90</v>
       </c>
       <c r="B90" t="s">
         <v>430</v>
       </c>
-      <c r="D90" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E90" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>91</v>
       </c>
       <c r="B91" t="s">
         <v>431</v>
       </c>
-      <c r="D91" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E91" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>92</v>
       </c>
       <c r="B92" t="s">
         <v>432</v>
       </c>
-      <c r="D92" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E92" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>93</v>
       </c>
       <c r="B93" t="s">
         <v>433</v>
       </c>
-      <c r="D93" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E93" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>94</v>
       </c>
       <c r="B94" t="s">
         <v>434</v>
       </c>
-      <c r="D94" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E94" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>95</v>
       </c>
       <c r="B95" t="s">
         <v>435</v>
       </c>
-      <c r="D95" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E95" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>96</v>
       </c>
       <c r="B96" t="s">
         <v>436</v>
       </c>
-      <c r="D96" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E96" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>97</v>
       </c>
       <c r="B97" t="s">
         <v>437</v>
       </c>
-      <c r="D97" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E97" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>98</v>
       </c>
       <c r="B98" t="s">
         <v>438</v>
       </c>
-      <c r="D98" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E98" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>99</v>
       </c>
       <c r="B99" t="s">
         <v>439</v>
       </c>
-      <c r="D99" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E99" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>100</v>
       </c>
       <c r="B100" t="s">
         <v>440</v>
       </c>
-      <c r="D100" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E100" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>101</v>
       </c>
       <c r="B101" t="s">
         <v>441</v>
       </c>
-      <c r="D101" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E101" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>102</v>
       </c>
       <c r="B102" t="s">
         <v>442</v>
       </c>
-      <c r="D102" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E102" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>103</v>
       </c>
       <c r="B103" t="s">
         <v>443</v>
       </c>
-      <c r="D103" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E103" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>104</v>
       </c>
       <c r="B104" t="s">
         <v>444</v>
       </c>
-      <c r="D104" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E104" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>105</v>
       </c>
       <c r="B105" t="s">
         <v>445</v>
       </c>
-      <c r="D105" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E105" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>106</v>
       </c>
       <c r="B106" t="s">
         <v>446</v>
       </c>
-      <c r="D106" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E106" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>107</v>
       </c>
       <c r="B107" t="s">
         <v>447</v>
       </c>
-      <c r="D107" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E107" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>108</v>
       </c>
       <c r="B108" t="s">
         <v>448</v>
       </c>
-      <c r="D108" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E108" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>109</v>
       </c>
       <c r="B109" t="s">
         <v>449</v>
       </c>
-      <c r="D109" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E109" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>110</v>
       </c>
       <c r="B110" t="s">
         <v>450</v>
       </c>
-      <c r="C110" t="s">
-        <v>451</v>
-      </c>
-      <c r="D110" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E110" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>111</v>
       </c>
       <c r="B111" t="s">
         <v>451</v>
       </c>
+      <c r="C111" t="s">
+        <v>820</v>
+      </c>
       <c r="D111" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+        <v>826</v>
+      </c>
+      <c r="E111" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>112</v>
       </c>
       <c r="B112" t="s">
         <v>452</v>
       </c>
-      <c r="D112" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E112" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>113</v>
       </c>
       <c r="B113" t="s">
         <v>453</v>
       </c>
-      <c r="D113" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E113" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>114</v>
       </c>
       <c r="B114" t="s">
         <v>454</v>
       </c>
-      <c r="D114" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E114" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>115</v>
       </c>
       <c r="B115" t="s">
         <v>455</v>
       </c>
-      <c r="D115" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E115" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>116</v>
       </c>
       <c r="B116" t="s">
         <v>456</v>
       </c>
-      <c r="D116" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E116" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>117</v>
       </c>
       <c r="B117" t="s">
         <v>457</v>
       </c>
-      <c r="D117" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E117" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>118</v>
       </c>
       <c r="B118" t="s">
         <v>458</v>
       </c>
-      <c r="D118" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E118" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>119</v>
       </c>
       <c r="B119" t="s">
         <v>459</v>
       </c>
-      <c r="D119" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E119" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>120</v>
       </c>
       <c r="B120" t="s">
         <v>460</v>
       </c>
-      <c r="D120" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E120" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>121</v>
       </c>
       <c r="B121" t="s">
         <v>461</v>
       </c>
-      <c r="D121" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E121" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>122</v>
       </c>
       <c r="B122" t="s">
         <v>462</v>
       </c>
-      <c r="D122" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E122" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>123</v>
       </c>
       <c r="B123" t="s">
         <v>463</v>
       </c>
-      <c r="D123" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E123" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>124</v>
       </c>
       <c r="B124" t="s">
         <v>464</v>
       </c>
-      <c r="D124" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E124" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>125</v>
       </c>
       <c r="B125" t="s">
         <v>465</v>
       </c>
-      <c r="D125" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E125" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>126</v>
       </c>
       <c r="B126" t="s">
         <v>466</v>
       </c>
-      <c r="D126" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E126" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>127</v>
       </c>
       <c r="B127" t="s">
         <v>467</v>
       </c>
-      <c r="D127" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E127" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>128</v>
       </c>
       <c r="B128" t="s">
         <v>468</v>
       </c>
+      <c r="C128" t="s">
+        <v>820</v>
+      </c>
       <c r="D128" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+        <v>827</v>
+      </c>
+      <c r="E128" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>129</v>
       </c>
       <c r="B129" t="s">
         <v>469</v>
       </c>
-      <c r="D129" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E129" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>130</v>
       </c>
       <c r="B130" t="s">
         <v>470</v>
       </c>
-      <c r="D130" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E130" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>131</v>
       </c>
       <c r="B131" t="s">
         <v>471</v>
       </c>
-      <c r="D131" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E131" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>132</v>
       </c>
       <c r="B132" t="s">
         <v>472</v>
       </c>
-      <c r="D132" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E132" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>133</v>
       </c>
       <c r="B133" t="s">
         <v>473</v>
       </c>
-      <c r="D133" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E133" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>134</v>
       </c>
       <c r="B134" t="s">
         <v>474</v>
       </c>
-      <c r="D134" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E134" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>135</v>
       </c>
       <c r="B135" t="s">
         <v>475</v>
       </c>
-      <c r="D135" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E135" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>136</v>
       </c>
       <c r="B136" t="s">
         <v>476</v>
       </c>
-      <c r="D136" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E136" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>137</v>
       </c>
       <c r="B137" t="s">
         <v>477</v>
       </c>
-      <c r="D137" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E137" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>138</v>
       </c>
       <c r="B138" t="s">
         <v>478</v>
       </c>
-      <c r="D138" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E138" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>139</v>
       </c>
       <c r="B139" t="s">
         <v>479</v>
       </c>
-      <c r="D139" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E139" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>140</v>
       </c>
       <c r="B140" t="s">
         <v>480</v>
       </c>
-      <c r="D140" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E140" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>141</v>
       </c>
       <c r="B141" t="s">
         <v>481</v>
       </c>
-      <c r="D141" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E141" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>142</v>
       </c>
       <c r="B142" t="s">
         <v>482</v>
       </c>
-      <c r="D142" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E142" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>143</v>
       </c>
       <c r="B143" t="s">
         <v>483</v>
       </c>
-      <c r="D143" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E143" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>144</v>
       </c>
       <c r="B144" t="s">
         <v>484</v>
       </c>
-      <c r="D144" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E144" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>145</v>
       </c>
       <c r="B145" t="s">
         <v>485</v>
       </c>
-      <c r="D145" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E145" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>146</v>
       </c>
       <c r="B146" t="s">
         <v>486</v>
       </c>
-      <c r="D146" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E146" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>147</v>
       </c>
       <c r="B147" t="s">
         <v>487</v>
       </c>
-      <c r="D147" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E147" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>148</v>
       </c>
       <c r="B148" t="s">
         <v>488</v>
       </c>
-      <c r="D148" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E148" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>149</v>
       </c>
       <c r="B149" t="s">
         <v>489</v>
       </c>
-      <c r="D149" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E149" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>150</v>
       </c>
       <c r="B150" t="s">
         <v>490</v>
       </c>
-      <c r="D150" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E150" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>151</v>
       </c>
       <c r="B151" t="s">
         <v>491</v>
       </c>
-      <c r="D151" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E151" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>152</v>
       </c>
       <c r="B152" t="s">
         <v>492</v>
       </c>
-      <c r="D152" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E152" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>153</v>
       </c>
       <c r="B153" t="s">
         <v>493</v>
       </c>
-      <c r="D153" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E153" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>154</v>
       </c>
       <c r="B154" t="s">
         <v>494</v>
       </c>
-      <c r="D154" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E154" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>155</v>
       </c>
       <c r="B155" t="s">
         <v>495</v>
       </c>
-      <c r="D155" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E155" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>156</v>
       </c>
       <c r="B156" t="s">
         <v>496</v>
       </c>
-      <c r="D156" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E156" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>157</v>
       </c>
       <c r="B157" t="s">
         <v>497</v>
       </c>
-      <c r="D157" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E157" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>158</v>
       </c>
       <c r="B158" t="s">
         <v>498</v>
       </c>
+      <c r="C158" t="s">
+        <v>820</v>
+      </c>
       <c r="D158" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+        <v>826</v>
+      </c>
+      <c r="E158" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>159</v>
       </c>
       <c r="B159" t="s">
         <v>499</v>
       </c>
-      <c r="D159" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E159" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>160</v>
       </c>
       <c r="B160" t="s">
         <v>500</v>
       </c>
-      <c r="D160" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E160" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>161</v>
       </c>
       <c r="B161" t="s">
         <v>501</v>
       </c>
-      <c r="D161" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E161" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>162</v>
       </c>
       <c r="B162" t="s">
         <v>502</v>
       </c>
-      <c r="D162" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E162" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>163</v>
       </c>
       <c r="B163" t="s">
         <v>503</v>
       </c>
-      <c r="D163" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E163" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>164</v>
       </c>
       <c r="B164" t="s">
         <v>504</v>
       </c>
-      <c r="D164" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E164" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>165</v>
       </c>
       <c r="B165" t="s">
         <v>505</v>
       </c>
-      <c r="D165" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E165" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>166</v>
       </c>
       <c r="B166" t="s">
         <v>506</v>
       </c>
-      <c r="D166" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E166" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>167</v>
       </c>
       <c r="B167" t="s">
         <v>507</v>
       </c>
-      <c r="D167" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E167" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>168</v>
       </c>
       <c r="B168" t="s">
         <v>508</v>
       </c>
-      <c r="D168" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E168" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>169</v>
       </c>
       <c r="B169" t="s">
         <v>509</v>
       </c>
-      <c r="D169" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E169" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>170</v>
       </c>
       <c r="B170" t="s">
         <v>510</v>
       </c>
-      <c r="D170" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E170" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>171</v>
       </c>
       <c r="B171" t="s">
         <v>511</v>
       </c>
-      <c r="D171" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E171" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>172</v>
       </c>
       <c r="B172" t="s">
         <v>512</v>
       </c>
-      <c r="D172" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E172" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>173</v>
       </c>
       <c r="B173" t="s">
         <v>513</v>
       </c>
-      <c r="D173" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E173" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>174</v>
       </c>
       <c r="B174" t="s">
         <v>514</v>
       </c>
-      <c r="D174" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E174" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>175</v>
       </c>
       <c r="B175" t="s">
         <v>515</v>
       </c>
-      <c r="D175" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E175" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>176</v>
       </c>
       <c r="B176" t="s">
         <v>516</v>
       </c>
-      <c r="D176" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E176" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>177</v>
       </c>
       <c r="B177" t="s">
         <v>517</v>
       </c>
-      <c r="D177" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E177" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>178</v>
       </c>
       <c r="B178" t="s">
         <v>518</v>
       </c>
-      <c r="D178" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E178" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>179</v>
       </c>
       <c r="B179" t="s">
         <v>519</v>
       </c>
-      <c r="D179" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E179" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>180</v>
       </c>
       <c r="B180" t="s">
         <v>520</v>
       </c>
-      <c r="D180" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E180" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>181</v>
       </c>
@@ -5249,1781 +5560,1920 @@
         <v>521</v>
       </c>
       <c r="C181" t="s">
-        <v>521</v>
+        <v>820</v>
       </c>
       <c r="D181" t="s">
+        <v>828</v>
+      </c>
+      <c r="E181" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>182</v>
       </c>
       <c r="B182" t="s">
         <v>522</v>
       </c>
-      <c r="D182" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E182" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>183</v>
       </c>
       <c r="B183" t="s">
         <v>523</v>
       </c>
-      <c r="D183" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E183" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>184</v>
       </c>
       <c r="B184" t="s">
         <v>524</v>
       </c>
-      <c r="D184" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E184" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>185</v>
       </c>
       <c r="B185" t="s">
         <v>525</v>
       </c>
-      <c r="D185" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E185" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>186</v>
       </c>
       <c r="B186" t="s">
         <v>526</v>
       </c>
-      <c r="D186" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E186" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>187</v>
       </c>
       <c r="B187" t="s">
         <v>527</v>
       </c>
-      <c r="D187" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E187" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>188</v>
       </c>
       <c r="B188" t="s">
         <v>528</v>
       </c>
-      <c r="D188" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E188" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>189</v>
       </c>
       <c r="B189" t="s">
         <v>529</v>
       </c>
-      <c r="D189" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E189" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>190</v>
       </c>
       <c r="B190" t="s">
         <v>530</v>
       </c>
-      <c r="D190" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E190" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>191</v>
       </c>
       <c r="B191" t="s">
         <v>531</v>
       </c>
-      <c r="D191" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E191" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>192</v>
       </c>
       <c r="B192" t="s">
         <v>532</v>
       </c>
-      <c r="D192" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E192" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>193</v>
       </c>
       <c r="B193" t="s">
         <v>533</v>
       </c>
-      <c r="D193" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E193" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>194</v>
       </c>
       <c r="B194" t="s">
         <v>534</v>
       </c>
-      <c r="D194" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E194" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>195</v>
       </c>
       <c r="B195" t="s">
         <v>535</v>
       </c>
-      <c r="D195" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E195" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>196</v>
       </c>
       <c r="B196" t="s">
         <v>536</v>
       </c>
+      <c r="C196" t="s">
+        <v>820</v>
+      </c>
       <c r="D196" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+        <v>828</v>
+      </c>
+      <c r="E196" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>197</v>
       </c>
       <c r="B197" t="s">
         <v>537</v>
       </c>
-      <c r="D197" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E197" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>198</v>
       </c>
       <c r="B198" t="s">
         <v>538</v>
       </c>
-      <c r="D198" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E198" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>199</v>
       </c>
       <c r="B199" t="s">
         <v>539</v>
       </c>
-      <c r="D199" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E199" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>200</v>
       </c>
       <c r="B200" t="s">
         <v>540</v>
       </c>
-      <c r="D200" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E200" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>201</v>
       </c>
       <c r="B201" t="s">
         <v>541</v>
       </c>
-      <c r="D201" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E201" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>202</v>
       </c>
       <c r="B202" t="s">
         <v>542</v>
       </c>
-      <c r="D202" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E202" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>203</v>
       </c>
       <c r="B203" t="s">
         <v>543</v>
       </c>
-      <c r="D203" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E203" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>204</v>
       </c>
       <c r="B204" t="s">
         <v>544</v>
       </c>
-      <c r="D204" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E204" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>205</v>
       </c>
       <c r="B205" t="s">
         <v>545</v>
       </c>
-      <c r="D205" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E205" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>206</v>
       </c>
       <c r="B206" t="s">
         <v>546</v>
       </c>
-      <c r="D206" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E206" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>207</v>
       </c>
       <c r="B207" t="s">
         <v>547</v>
       </c>
-      <c r="D207" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E207" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>208</v>
       </c>
       <c r="B208" t="s">
         <v>548</v>
       </c>
-      <c r="D208" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E208" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>209</v>
       </c>
       <c r="B209" t="s">
         <v>549</v>
       </c>
-      <c r="D209" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E209" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>210</v>
       </c>
       <c r="B210" t="s">
         <v>550</v>
       </c>
-      <c r="D210" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E210" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>211</v>
       </c>
       <c r="B211" t="s">
         <v>551</v>
       </c>
-      <c r="D211" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E211" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>212</v>
       </c>
       <c r="B212" t="s">
         <v>552</v>
       </c>
-      <c r="D212" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E212" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>213</v>
       </c>
       <c r="B213" t="s">
         <v>553</v>
       </c>
-      <c r="D213" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E213" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>214</v>
       </c>
       <c r="B214" t="s">
         <v>554</v>
       </c>
-      <c r="D214" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E214" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>215</v>
       </c>
       <c r="B215" t="s">
         <v>555</v>
       </c>
-      <c r="D215" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E215" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>216</v>
       </c>
       <c r="B216" t="s">
         <v>556</v>
       </c>
-      <c r="D216" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E216" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>217</v>
       </c>
       <c r="B217" t="s">
         <v>557</v>
       </c>
-      <c r="D217" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E217" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>218</v>
       </c>
       <c r="B218" t="s">
         <v>558</v>
       </c>
-      <c r="D218" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E218" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>219</v>
       </c>
       <c r="B219" t="s">
         <v>559</v>
       </c>
-      <c r="D219" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E219" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>220</v>
       </c>
       <c r="B220" t="s">
         <v>560</v>
       </c>
-      <c r="D220" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E220" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>221</v>
       </c>
       <c r="B221" t="s">
         <v>561</v>
       </c>
-      <c r="D221" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E221" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>222</v>
       </c>
       <c r="B222" t="s">
         <v>562</v>
       </c>
-      <c r="D222" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E222" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>223</v>
       </c>
       <c r="B223" t="s">
         <v>563</v>
       </c>
+      <c r="C223" t="s">
+        <v>820</v>
+      </c>
       <c r="D223" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+        <v>563</v>
+      </c>
+      <c r="E223" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>224</v>
       </c>
       <c r="B224" t="s">
         <v>564</v>
       </c>
-      <c r="D224" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E224" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>225</v>
       </c>
       <c r="B225" t="s">
         <v>565</v>
       </c>
-      <c r="D225" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E225" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>226</v>
       </c>
       <c r="B226" t="s">
         <v>566</v>
       </c>
-      <c r="D226" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E226" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>227</v>
       </c>
       <c r="B227" t="s">
         <v>567</v>
       </c>
-      <c r="D227" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E227" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>228</v>
       </c>
       <c r="B228" t="s">
         <v>568</v>
       </c>
-      <c r="D228" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E228" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>229</v>
       </c>
       <c r="B229" t="s">
         <v>569</v>
       </c>
-      <c r="D229" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E229" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>230</v>
       </c>
       <c r="B230" t="s">
         <v>570</v>
       </c>
-      <c r="D230" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E230" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>231</v>
       </c>
       <c r="B231" t="s">
         <v>571</v>
       </c>
-      <c r="D231" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E231" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>232</v>
       </c>
       <c r="B232" t="s">
         <v>572</v>
       </c>
-      <c r="D232" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E232" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>233</v>
       </c>
       <c r="B233" t="s">
         <v>573</v>
       </c>
-      <c r="D233" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E233" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>234</v>
       </c>
       <c r="B234" t="s">
         <v>574</v>
       </c>
-      <c r="D234" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E234" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>235</v>
       </c>
       <c r="B235" t="s">
         <v>575</v>
       </c>
-      <c r="D235" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E235" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>236</v>
       </c>
       <c r="B236" t="s">
         <v>576</v>
       </c>
-      <c r="D236" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E236" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>237</v>
       </c>
       <c r="B237" t="s">
         <v>577</v>
       </c>
-      <c r="D237" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E237" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>238</v>
       </c>
       <c r="B238" t="s">
         <v>578</v>
       </c>
-      <c r="D238" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E238" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>239</v>
       </c>
       <c r="B239" t="s">
         <v>579</v>
       </c>
-      <c r="D239" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E239" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>240</v>
       </c>
       <c r="B240" t="s">
         <v>580</v>
       </c>
-      <c r="D240" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E240" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>241</v>
       </c>
       <c r="B241" t="s">
         <v>581</v>
       </c>
-      <c r="D241" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E241" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>242</v>
       </c>
       <c r="B242" t="s">
         <v>582</v>
       </c>
-      <c r="D242" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E242" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>243</v>
       </c>
       <c r="B243" t="s">
         <v>583</v>
       </c>
-      <c r="D243" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E243" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>244</v>
       </c>
       <c r="B244" t="s">
         <v>584</v>
       </c>
-      <c r="D244" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E244" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>245</v>
       </c>
       <c r="B245" t="s">
         <v>585</v>
       </c>
-      <c r="D245" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E245" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>246</v>
       </c>
       <c r="B246" t="s">
         <v>586</v>
       </c>
-      <c r="D246" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E246" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>247</v>
       </c>
       <c r="B247" t="s">
         <v>587</v>
       </c>
-      <c r="D247" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E247" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>248</v>
       </c>
       <c r="B248" t="s">
         <v>588</v>
       </c>
-      <c r="D248" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E248" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>249</v>
       </c>
       <c r="B249" t="s">
         <v>589</v>
       </c>
-      <c r="D249" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E249" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>250</v>
       </c>
       <c r="B250" t="s">
         <v>590</v>
       </c>
+      <c r="C250" t="s">
+        <v>820</v>
+      </c>
       <c r="D250" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+        <v>806</v>
+      </c>
+      <c r="E250" t="s">
+        <v>737</v>
+      </c>
+      <c r="F250" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>251</v>
       </c>
       <c r="B251" t="s">
         <v>591</v>
       </c>
-      <c r="D251" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E251" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>252</v>
       </c>
       <c r="B252" t="s">
         <v>592</v>
       </c>
-      <c r="D252" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E252" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>253</v>
       </c>
       <c r="B253" t="s">
         <v>593</v>
       </c>
-      <c r="D253" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E253" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>254</v>
       </c>
       <c r="B254" t="s">
         <v>594</v>
       </c>
-      <c r="D254" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E254" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>255</v>
       </c>
       <c r="B255" t="s">
         <v>595</v>
       </c>
+      <c r="C255" t="s">
+        <v>820</v>
+      </c>
       <c r="D255" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+        <v>830</v>
+      </c>
+      <c r="E255" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>256</v>
       </c>
       <c r="B256" t="s">
         <v>596</v>
       </c>
-      <c r="D256" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E256" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>257</v>
       </c>
       <c r="B257" t="s">
         <v>597</v>
       </c>
-      <c r="D257" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E257" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>258</v>
       </c>
       <c r="B258" t="s">
         <v>598</v>
       </c>
-      <c r="D258" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E258" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>259</v>
       </c>
       <c r="B259" t="s">
         <v>599</v>
       </c>
-      <c r="D259" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E259" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>260</v>
       </c>
       <c r="B260" t="s">
         <v>600</v>
       </c>
-      <c r="D260" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E260" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>261</v>
       </c>
       <c r="B261" t="s">
         <v>601</v>
       </c>
-      <c r="D261" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E261" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>262</v>
       </c>
       <c r="B262" t="s">
         <v>602</v>
       </c>
-      <c r="D262" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E262" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>263</v>
       </c>
       <c r="B263" t="s">
         <v>603</v>
       </c>
-      <c r="D263" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E263" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>264</v>
       </c>
       <c r="B264" t="s">
         <v>604</v>
       </c>
-      <c r="D264" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E264" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>265</v>
       </c>
       <c r="B265" t="s">
         <v>605</v>
       </c>
-      <c r="D265" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E265" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>266</v>
       </c>
       <c r="B266" t="s">
         <v>606</v>
       </c>
-      <c r="D266" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E266" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>267</v>
       </c>
       <c r="B267" t="s">
         <v>607</v>
       </c>
-      <c r="D267" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E267" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>268</v>
       </c>
       <c r="B268" t="s">
         <v>608</v>
       </c>
-      <c r="D268" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E268" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>269</v>
       </c>
       <c r="B269" t="s">
         <v>609</v>
       </c>
-      <c r="D269" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E269" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>270</v>
       </c>
       <c r="B270" t="s">
         <v>610</v>
       </c>
-      <c r="D270" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E270" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>271</v>
       </c>
       <c r="B271" t="s">
         <v>611</v>
       </c>
-      <c r="D271" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E271" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>272</v>
       </c>
       <c r="B272" t="s">
         <v>612</v>
       </c>
-      <c r="D272" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E272" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>273</v>
       </c>
       <c r="B273" t="s">
         <v>613</v>
       </c>
-      <c r="D273" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E273" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>274</v>
       </c>
       <c r="B274" t="s">
         <v>614</v>
       </c>
-      <c r="D274" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E274" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>275</v>
       </c>
       <c r="B275" t="s">
         <v>615</v>
       </c>
-      <c r="D275" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E275" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>276</v>
       </c>
       <c r="B276" t="s">
         <v>616</v>
       </c>
-      <c r="D276" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E276" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>277</v>
       </c>
       <c r="B277" t="s">
         <v>617</v>
       </c>
-      <c r="D277" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E277" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>278</v>
       </c>
       <c r="B278" t="s">
         <v>618</v>
       </c>
-      <c r="D278" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E278" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>279</v>
       </c>
       <c r="B279" t="s">
         <v>619</v>
       </c>
+      <c r="C279" t="s">
+        <v>820</v>
+      </c>
       <c r="D279" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+        <v>831</v>
+      </c>
+      <c r="E279" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>280</v>
       </c>
       <c r="B280" t="s">
         <v>620</v>
       </c>
-      <c r="D280" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E280" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>281</v>
       </c>
       <c r="B281" t="s">
         <v>621</v>
       </c>
-      <c r="D281" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E281" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>282</v>
       </c>
       <c r="B282" t="s">
         <v>622</v>
       </c>
-      <c r="D282" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E282" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>283</v>
       </c>
       <c r="B283" t="s">
         <v>623</v>
       </c>
-      <c r="D283" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E283" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>284</v>
       </c>
       <c r="B284" t="s">
         <v>624</v>
       </c>
-      <c r="D284" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E284" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>285</v>
       </c>
       <c r="B285" t="s">
         <v>625</v>
       </c>
-      <c r="D285" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E285" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>286</v>
       </c>
       <c r="B286" t="s">
         <v>626</v>
       </c>
-      <c r="D286" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E286" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>287</v>
       </c>
       <c r="B287" t="s">
         <v>627</v>
       </c>
-      <c r="D287" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E287" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>288</v>
       </c>
       <c r="B288" t="s">
         <v>628</v>
       </c>
-      <c r="D288" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E288" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>289</v>
       </c>
       <c r="B289" t="s">
         <v>629</v>
       </c>
-      <c r="D289" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E289" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>290</v>
       </c>
       <c r="B290" t="s">
         <v>630</v>
       </c>
-      <c r="D290" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E290" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>291</v>
       </c>
       <c r="B291" t="s">
         <v>631</v>
       </c>
-      <c r="D291" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E291" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>292</v>
       </c>
       <c r="B292" t="s">
         <v>632</v>
       </c>
-      <c r="D292" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E292" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>293</v>
       </c>
       <c r="B293" t="s">
         <v>633</v>
       </c>
-      <c r="D293" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E293" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>294</v>
       </c>
       <c r="B294" t="s">
         <v>634</v>
       </c>
-      <c r="D294" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E294" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>295</v>
       </c>
       <c r="B295" t="s">
         <v>635</v>
       </c>
-      <c r="D295" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E295" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>296</v>
       </c>
       <c r="B296" t="s">
         <v>636</v>
       </c>
-      <c r="D296" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E296" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>297</v>
       </c>
       <c r="B297" t="s">
         <v>637</v>
       </c>
-      <c r="D297" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E297" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>298</v>
       </c>
       <c r="B298" t="s">
         <v>638</v>
       </c>
-      <c r="D298" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E298" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>299</v>
       </c>
       <c r="B299" t="s">
         <v>639</v>
       </c>
-      <c r="D299" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E299" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>300</v>
       </c>
       <c r="B300" t="s">
         <v>640</v>
       </c>
-      <c r="D300" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E300" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>301</v>
       </c>
       <c r="B301" t="s">
         <v>641</v>
       </c>
-      <c r="D301" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E301" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>302</v>
       </c>
       <c r="B302" t="s">
         <v>642</v>
       </c>
-      <c r="D302" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E302" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>303</v>
       </c>
       <c r="B303" t="s">
         <v>643</v>
       </c>
+      <c r="C303" t="s">
+        <v>820</v>
+      </c>
       <c r="D303" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
+        <v>643</v>
+      </c>
+      <c r="E303" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>304</v>
       </c>
       <c r="B304" t="s">
         <v>644</v>
       </c>
-      <c r="D304" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E304" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>305</v>
       </c>
       <c r="B305" t="s">
         <v>645</v>
       </c>
-      <c r="D305" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E305" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>306</v>
       </c>
       <c r="B306" t="s">
         <v>646</v>
       </c>
-      <c r="D306" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E306" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>307</v>
       </c>
       <c r="B307" t="s">
         <v>647</v>
       </c>
-      <c r="D307" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E307" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>308</v>
       </c>
       <c r="B308" t="s">
         <v>648</v>
       </c>
-      <c r="D308" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E308" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>309</v>
       </c>
       <c r="B309" t="s">
         <v>649</v>
       </c>
-      <c r="D309" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E309" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>310</v>
       </c>
       <c r="B310" t="s">
         <v>650</v>
       </c>
-      <c r="D310" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E310" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>311</v>
       </c>
       <c r="B311" t="s">
         <v>651</v>
       </c>
-      <c r="D311" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E311" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>312</v>
       </c>
       <c r="B312" t="s">
         <v>652</v>
       </c>
-      <c r="D312" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E312" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>313</v>
       </c>
       <c r="B313" t="s">
         <v>653</v>
       </c>
-      <c r="D313" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E313" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>314</v>
       </c>
       <c r="B314" t="s">
         <v>654</v>
       </c>
-      <c r="D314" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E314" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>315</v>
       </c>
       <c r="B315" t="s">
         <v>655</v>
       </c>
-      <c r="D315" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E315" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>316</v>
       </c>
       <c r="B316" t="s">
         <v>656</v>
       </c>
-      <c r="D316" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E316" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>317</v>
       </c>
       <c r="B317" t="s">
         <v>657</v>
       </c>
-      <c r="D317" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E317" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>318</v>
       </c>
       <c r="B318" t="s">
         <v>658</v>
       </c>
+      <c r="C318" t="s">
+        <v>837</v>
+      </c>
       <c r="D318" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
+        <v>658</v>
+      </c>
+      <c r="E318" t="s">
+        <v>737</v>
+      </c>
+      <c r="F318" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>319</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B319" s="7" t="s">
         <v>659</v>
       </c>
+      <c r="C319" t="s">
+        <v>820</v>
+      </c>
       <c r="D319" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
+        <v>659</v>
+      </c>
+      <c r="E319" t="s">
+        <v>737</v>
+      </c>
+      <c r="F319" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>320</v>
       </c>
       <c r="B320" t="s">
         <v>660</v>
       </c>
-      <c r="D320" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E320" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>321</v>
       </c>
       <c r="B321" t="s">
         <v>661</v>
       </c>
-      <c r="D321" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E321" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>322</v>
       </c>
       <c r="B322" t="s">
         <v>662</v>
       </c>
-      <c r="D322" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E322" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>323</v>
       </c>
-      <c r="B323" t="s">
+      <c r="B323" s="7" t="s">
         <v>663</v>
       </c>
+      <c r="C323" t="s">
+        <v>820</v>
+      </c>
       <c r="D323" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
+        <v>830</v>
+      </c>
+      <c r="E323" t="s">
+        <v>737</v>
+      </c>
+      <c r="F323" s="6" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>324</v>
       </c>
       <c r="B324" t="s">
         <v>664</v>
       </c>
-      <c r="D324" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E324" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>325</v>
       </c>
       <c r="B325" t="s">
         <v>665</v>
       </c>
-      <c r="D325" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E325" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>326</v>
       </c>
       <c r="B326" t="s">
         <v>666</v>
       </c>
-      <c r="D326" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E326" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>327</v>
       </c>
       <c r="B327" t="s">
         <v>667</v>
       </c>
-      <c r="D327" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E327" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>328</v>
       </c>
       <c r="B328" t="s">
         <v>668</v>
       </c>
-      <c r="D328" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E328" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>329</v>
       </c>
       <c r="B329" t="s">
         <v>669</v>
       </c>
+      <c r="C329" t="s">
+        <v>820</v>
+      </c>
       <c r="D329" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
+        <v>806</v>
+      </c>
+      <c r="E329" t="s">
+        <v>737</v>
+      </c>
+      <c r="F329" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>330</v>
       </c>
       <c r="B330" t="s">
         <v>670</v>
       </c>
-      <c r="D330" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E330" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>331</v>
       </c>
       <c r="B331" t="s">
         <v>671</v>
       </c>
+      <c r="C331" t="s">
+        <v>820</v>
+      </c>
       <c r="D331" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
+        <v>830</v>
+      </c>
+      <c r="E331" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>332</v>
       </c>
       <c r="B332" t="s">
         <v>672</v>
       </c>
+      <c r="C332" t="s">
+        <v>820</v>
+      </c>
       <c r="D332" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
+        <v>668</v>
+      </c>
+      <c r="E332" t="s">
+        <v>737</v>
+      </c>
+      <c r="F332" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>333</v>
       </c>
       <c r="B333" t="s">
         <v>673</v>
       </c>
-      <c r="D333" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E333" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>334</v>
       </c>
       <c r="B334" t="s">
         <v>674</v>
       </c>
-      <c r="D334" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E334" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>335</v>
       </c>
-      <c r="B335" t="s">
+      <c r="B335" s="6" t="s">
         <v>675</v>
       </c>
+      <c r="C335" t="s">
+        <v>820</v>
+      </c>
       <c r="D335" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
+        <v>806</v>
+      </c>
+      <c r="E335" t="s">
+        <v>737</v>
+      </c>
+      <c r="F335" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>336</v>
       </c>
       <c r="B336" t="s">
         <v>676</v>
       </c>
+      <c r="C336" t="s">
+        <v>820</v>
+      </c>
       <c r="D336" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
+        <v>673</v>
+      </c>
+      <c r="E336" t="s">
+        <v>737</v>
+      </c>
+      <c r="F336" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>337</v>
       </c>
       <c r="B337" t="s">
         <v>677</v>
       </c>
+      <c r="C337" t="s">
+        <v>820</v>
+      </c>
       <c r="D337" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
+        <v>826</v>
+      </c>
+      <c r="E337" t="s">
+        <v>737</v>
+      </c>
+      <c r="F337" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>338</v>
       </c>
       <c r="B338" t="s">
         <v>678</v>
       </c>
+      <c r="C338" t="s">
+        <v>820</v>
+      </c>
       <c r="D338" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
+        <v>830</v>
+      </c>
+      <c r="E338" t="s">
+        <v>737</v>
+      </c>
+      <c r="F338" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>339</v>
       </c>
-      <c r="B339" t="s">
+      <c r="B339" s="6" t="s">
         <v>679</v>
       </c>
       <c r="D339" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
+        <v>839</v>
+      </c>
+      <c r="E339" t="s">
+        <v>840</v>
+      </c>
+      <c r="F339" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>340</v>
       </c>
       <c r="B340" t="s">
         <v>680</v>
       </c>
-      <c r="D340" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E340" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>341</v>
       </c>
       <c r="B341" t="s">
         <v>681</v>
       </c>
-      <c r="D341" t="s">
+      <c r="E341" t="s">
         <v>738</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F23"/>
+  <sheetPr>
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.08984375" bestFit="1" customWidth="1"/>
@@ -7170,7 +7620,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>699</v>
       </c>
@@ -7178,7 +7628,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>700</v>
       </c>
@@ -7186,7 +7636,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>701</v>
       </c>
@@ -7194,15 +7644,18 @@
         <v>563</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>702</v>
       </c>
       <c r="B20" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="F20" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>703</v>
       </c>
@@ -7210,7 +7663,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>704</v>
       </c>
@@ -7218,12 +7671,20 @@
         <v>643</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>705</v>
       </c>
       <c r="B23" t="s">
         <v>658</v>
+      </c>
+      <c r="F23" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F24" t="s">
+        <v>811</v>
       </c>
     </row>
   </sheetData>
@@ -7232,8 +7693,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor theme="4"/>
+  </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7276,6 +7740,12 @@
       <c r="D2" t="s">
         <v>737</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -7413,4 +7883,269 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052CF2D8E3E532648A9A53BA8B542239D" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a1fb610553ec5defc474bb1f7a0ddc39">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9ce6b1c7-1e7d-4e54-8192-c843964c72a7" xmlns:ns3="4ae99fea-3ccc-4497-bfcd-e0cb757e7dff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d9d4414e518fb510d6d835712213802" ns2:_="" ns3:_="">
+    <xsd:import namespace="9ce6b1c7-1e7d-4e54-8192-c843964c72a7"/>
+    <xsd:import namespace="4ae99fea-3ccc-4497-bfcd-e0cb757e7dff"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9ce6b1c7-1e7d-4e54-8192-c843964c72a7" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="11" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d584d655-5024-4d02-a0e2-cce7bfaf8d12" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="19" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4ae99fea-3ccc-4497-bfcd-e0cb757e7dff" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{266ebaab-2d21-4238-9d04-68b2522a488b}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="4ae99fea-3ccc-4497-bfcd-e0cb757e7dff">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEFD0438-3B89-46D3-AFC2-2E1E8BA59BF1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF250B34-2756-44A2-A030-8FEBB211D63C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9ce6b1c7-1e7d-4e54-8192-c843964c72a7"/>
+    <ds:schemaRef ds:uri="4ae99fea-3ccc-4497-bfcd-e0cb757e7dff"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Indicator_Gen/Python Code/BLS/config/BLS_State and Area Employment_Series ID Codes.xlsx
+++ b/Indicator_Gen/Python Code/BLS/config/BLS_State and Area Employment_Series ID Codes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sacog.sharepoint.com/sites/RegionalMonitoringandReporting/Shared Documents/Process Revamp/Task 9. Collect new data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfontes\Documents\Projects\Regional-Monitoring\Indicator_Gen\Python Code\BLS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="13_ncr:1_{D11369E1-5776-4A57-BFA2-F789D30C5E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0331B726-895D-47CF-B0B4-0580987959CF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A8FD21-8E0A-4BB8-8EC8-71BA39C001B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="5" r:id="rId1"/>
@@ -2638,7 +2638,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2668,12 +2668,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2729,7 +2723,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2743,7 +2737,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7128,7 +7121,7 @@
       <c r="A319" t="s">
         <v>319</v>
       </c>
-      <c r="B319" s="7" t="s">
+      <c r="B319" t="s">
         <v>659</v>
       </c>
       <c r="C319" t="s">
@@ -7181,7 +7174,7 @@
       <c r="A323" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="7" t="s">
+      <c r="B323" t="s">
         <v>663</v>
       </c>
       <c r="C323" t="s">
@@ -7886,15 +7879,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052CF2D8E3E532648A9A53BA8B542239D" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a1fb610553ec5defc474bb1f7a0ddc39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9ce6b1c7-1e7d-4e54-8192-c843964c72a7" xmlns:ns3="4ae99fea-3ccc-4497-bfcd-e0cb757e7dff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d9d4414e518fb510d6d835712213802" ns2:_="" ns3:_="">
     <xsd:import namespace="9ce6b1c7-1e7d-4e54-8192-c843964c72a7"/>
@@ -8123,15 +8107,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEFD0438-3B89-46D3-AFC2-2E1E8BA59BF1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF250B34-2756-44A2-A030-8FEBB211D63C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8148,4 +8133,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEFD0438-3B89-46D3-AFC2-2E1E8BA59BF1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Indicator_Gen/Python Code/BLS/config/BLS_State and Area Employment_Series ID Codes.xlsx
+++ b/Indicator_Gen/Python Code/BLS/config/BLS_State and Area Employment_Series ID Codes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfontes\Documents\Projects\Regional-Monitoring\Indicator_Gen\Python Code\BLS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A8FD21-8E0A-4BB8-8EC8-71BA39C001B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27457B48-0650-405B-8F2D-5424527FAE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="5" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="835">
   <si>
     <t>industry_code</t>
   </si>
@@ -2343,12 +2343,6 @@
     <t>sp_folder</t>
   </si>
   <si>
-    <t>Themes</t>
-  </si>
-  <si>
-    <t>SharePoint Paths</t>
-  </si>
-  <si>
     <t>12420</t>
   </si>
   <si>
@@ -2358,12 +2352,6 @@
     <t>Vibrant and Inclusive Places</t>
   </si>
   <si>
-    <t>Economy\\Income</t>
-  </si>
-  <si>
-    <t>People and Community\\Pop and Demographics</t>
-  </si>
-  <si>
     <t>16740</t>
   </si>
   <si>
@@ -2379,18 +2367,12 @@
     <t>Cincinnati, OH-KY-IN Metro Area</t>
   </si>
   <si>
-    <t>Economy\\Education</t>
-  </si>
-  <si>
     <t>17460</t>
   </si>
   <si>
     <t>Cleveland-Elyria, OH Metro Area</t>
   </si>
   <si>
-    <t>People and Community\\Broadband</t>
-  </si>
-  <si>
     <t>18140</t>
   </si>
   <si>
@@ -2403,19 +2385,10 @@
     <t>Detroit-Warren-Dearborn, MI Metro Area</t>
   </si>
   <si>
-    <t>Next Gen of Mobility Solutions</t>
-  </si>
-  <si>
-    <t>Travel modes</t>
-  </si>
-  <si>
     <t>26900</t>
   </si>
   <si>
     <t>Indianapolis-Carmel-Anderson, IN Metro Area</t>
-  </si>
-  <si>
-    <t>People and Community\\Healthy Places</t>
   </si>
   <si>
     <t>28140</t>
@@ -3126,66 +3099,66 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="B10" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="B11" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B12" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
     </row>
   </sheetData>
@@ -3232,252 +3205,206 @@
       <c r="G1" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>748</v>
-      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C2" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="D2">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="E2">
         <v>2023</v>
       </c>
       <c r="F2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G2" t="s">
-        <v>756</v>
-      </c>
-      <c r="J2" t="s">
-        <v>751</v>
-      </c>
-      <c r="K2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B3" t="s">
-        <v>755</v>
-      </c>
-      <c r="J3" t="s">
         <v>751</v>
-      </c>
-      <c r="K3" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B4" t="s">
-        <v>758</v>
-      </c>
-      <c r="J4" t="s">
-        <v>751</v>
-      </c>
-      <c r="K4" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="B5" t="s">
-        <v>761</v>
-      </c>
-      <c r="J5" t="s">
-        <v>751</v>
-      </c>
-      <c r="K5" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="B6" t="s">
-        <v>764</v>
-      </c>
-      <c r="J6" t="s">
-        <v>751</v>
-      </c>
-      <c r="K6" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B7" t="s">
-        <v>766</v>
-      </c>
-      <c r="J7" t="s">
-        <v>767</v>
-      </c>
-      <c r="K7" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="B8" t="s">
-        <v>770</v>
-      </c>
-      <c r="J8" t="s">
-        <v>751</v>
-      </c>
-      <c r="K8" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="B9" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="B10" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="B11" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
       <c r="B12" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
       <c r="B13" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="B14" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="B15" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="B16" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="B17" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="B18" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
       <c r="B19" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="B20" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="B21" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="B22" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="B23" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="B24" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
     </row>
   </sheetData>
@@ -3507,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>736</v>
@@ -3530,13 +3457,13 @@
         <v>342</v>
       </c>
       <c r="C2" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="E2" t="s">
         <v>739</v>
       </c>
       <c r="G2" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -3547,13 +3474,13 @@
         <v>343</v>
       </c>
       <c r="C3" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="E3" t="s">
         <v>739</v>
       </c>
       <c r="G3" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -3564,7 +3491,7 @@
         <v>344</v>
       </c>
       <c r="C4" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="E4" t="s">
         <v>739</v>
@@ -3578,7 +3505,7 @@
         <v>345</v>
       </c>
       <c r="C5" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="E5" t="s">
         <v>739</v>
@@ -3603,7 +3530,7 @@
         <v>347</v>
       </c>
       <c r="C7" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D7" t="s">
         <v>347</v>
@@ -3730,7 +3657,7 @@
         <v>358</v>
       </c>
       <c r="C18" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D18" t="s">
         <v>358</v>
@@ -3890,7 +3817,7 @@
         <v>372</v>
       </c>
       <c r="C32" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D32" t="s">
         <v>372</v>
@@ -4765,10 +4692,10 @@
         <v>451</v>
       </c>
       <c r="C111" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D111" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="E111" t="s">
         <v>737</v>
@@ -4958,10 +4885,10 @@
         <v>468</v>
       </c>
       <c r="C128" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D128" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="E128" t="s">
         <v>737</v>
@@ -5294,10 +5221,10 @@
         <v>498</v>
       </c>
       <c r="C158" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D158" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="E158" t="s">
         <v>737</v>
@@ -5553,10 +5480,10 @@
         <v>521</v>
       </c>
       <c r="C181" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D181" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="E181" t="s">
         <v>737</v>
@@ -5724,10 +5651,10 @@
         <v>536</v>
       </c>
       <c r="C196" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D196" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="E196" t="s">
         <v>737</v>
@@ -6027,7 +5954,7 @@
         <v>563</v>
       </c>
       <c r="C223" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D223" t="s">
         <v>563</v>
@@ -6330,16 +6257,16 @@
         <v>590</v>
       </c>
       <c r="C250" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D250" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="E250" t="s">
         <v>737</v>
       </c>
       <c r="F250" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.35">
@@ -6350,7 +6277,7 @@
         <v>591</v>
       </c>
       <c r="E251" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
@@ -6361,7 +6288,7 @@
         <v>592</v>
       </c>
       <c r="E252" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
@@ -6372,7 +6299,7 @@
         <v>593</v>
       </c>
       <c r="E253" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
@@ -6383,7 +6310,7 @@
         <v>594</v>
       </c>
       <c r="E254" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
@@ -6394,10 +6321,10 @@
         <v>595</v>
       </c>
       <c r="C255" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D255" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="E255" t="s">
         <v>737</v>
@@ -6664,10 +6591,10 @@
         <v>619</v>
       </c>
       <c r="C279" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D279" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="E279" t="s">
         <v>737</v>
@@ -6934,7 +6861,7 @@
         <v>643</v>
       </c>
       <c r="C303" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D303" t="s">
         <v>643</v>
@@ -7105,7 +7032,7 @@
         <v>658</v>
       </c>
       <c r="C318" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="D318" t="s">
         <v>658</v>
@@ -7114,7 +7041,7 @@
         <v>737</v>
       </c>
       <c r="F318" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.35">
@@ -7125,7 +7052,7 @@
         <v>659</v>
       </c>
       <c r="C319" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D319" t="s">
         <v>659</v>
@@ -7134,7 +7061,7 @@
         <v>737</v>
       </c>
       <c r="F319" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.35">
@@ -7178,16 +7105,16 @@
         <v>663</v>
       </c>
       <c r="C323" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D323" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="E323" t="s">
         <v>737</v>
       </c>
       <c r="F323" s="6" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.35">
@@ -7253,16 +7180,16 @@
         <v>669</v>
       </c>
       <c r="C329" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D329" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="E329" t="s">
         <v>737</v>
       </c>
       <c r="F329" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
@@ -7284,10 +7211,10 @@
         <v>671</v>
       </c>
       <c r="C331" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D331" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="E331" t="s">
         <v>737</v>
@@ -7301,7 +7228,7 @@
         <v>672</v>
       </c>
       <c r="C332" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D332" t="s">
         <v>668</v>
@@ -7310,7 +7237,7 @@
         <v>737</v>
       </c>
       <c r="F332" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.35">
@@ -7343,16 +7270,16 @@
         <v>675</v>
       </c>
       <c r="C335" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D335" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="E335" t="s">
         <v>737</v>
       </c>
       <c r="F335" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.35">
@@ -7363,7 +7290,7 @@
         <v>676</v>
       </c>
       <c r="C336" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D336" t="s">
         <v>673</v>
@@ -7372,7 +7299,7 @@
         <v>737</v>
       </c>
       <c r="F336" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.35">
@@ -7383,16 +7310,16 @@
         <v>677</v>
       </c>
       <c r="C337" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D337" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="E337" t="s">
         <v>737</v>
       </c>
       <c r="F337" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.35">
@@ -7403,16 +7330,16 @@
         <v>678</v>
       </c>
       <c r="C338" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D338" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="E338" t="s">
         <v>737</v>
       </c>
       <c r="F338" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
@@ -7423,13 +7350,13 @@
         <v>679</v>
       </c>
       <c r="D339" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="E339" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
       <c r="F339" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.35">
@@ -7645,7 +7572,7 @@
         <v>708</v>
       </c>
       <c r="F20" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -7672,12 +7599,12 @@
         <v>658</v>
       </c>
       <c r="F23" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="F24" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -7728,7 +7655,7 @@
         <v>720</v>
       </c>
       <c r="C2" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="D2" t="s">
         <v>737</v>
@@ -7737,7 +7664,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -7879,6 +7806,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052CF2D8E3E532648A9A53BA8B542239D" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a1fb610553ec5defc474bb1f7a0ddc39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9ce6b1c7-1e7d-4e54-8192-c843964c72a7" xmlns:ns3="4ae99fea-3ccc-4497-bfcd-e0cb757e7dff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d9d4414e518fb510d6d835712213802" ns2:_="" ns3:_="">
     <xsd:import namespace="9ce6b1c7-1e7d-4e54-8192-c843964c72a7"/>
@@ -8107,16 +8043,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEFD0438-3B89-46D3-AFC2-2E1E8BA59BF1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF250B34-2756-44A2-A030-8FEBB211D63C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8133,12 +8068,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEFD0438-3B89-46D3-AFC2-2E1E8BA59BF1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>